--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>94.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>83.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>10.5</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (14)</t>
+          <t>Q4 (13.5)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-17)</t>
+          <t>Q2 (-2.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,29 +701,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (14)</t>
+          <t>Diff médio casa: 34 | fora: -13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>resultado</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Diff médio em vitórias: 34 | em derrotas: -13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>períodos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pior período: Q2 (-17)</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Melhor período: Q4 (13.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q2 (-2.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A. Moreira sobe mais em vitórias (8 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,8 +864,41 @@
         <v>-13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,234 +997,346 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
       <c r="E2" t="n">
-        <v>22.2</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>-16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
+      </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>-16</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>28</v>
+      </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>30.3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28</v>
+      </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. Silva</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
       <c r="E4" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32</v>
+      </c>
       <c r="J4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>M. Correia</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
       <c r="E5" t="n">
-        <v>22.7</v>
+        <v>25.1</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>-11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-11</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>27.5</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>-21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>-21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Correia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
       <c r="E7" t="n">
-        <v>25.1</v>
+        <v>30.8</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>-11</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22</v>
+      </c>
       <c r="E8" t="n">
-        <v>30.3</v>
+        <v>24.1</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>22</v>
+      </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. Panov</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
       <c r="E9" t="n">
-        <v>27.5</v>
+        <v>22.7</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>-21</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>-10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>-10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1260,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
       <c r="J2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="H3" t="n">
-        <v>-17</v>
+        <v>-5</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>26</v>
+        <v>23.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-17</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
+        <v>62</v>
+      </c>
+      <c r="G5" t="n">
         <v>35</v>
       </c>
-      <c r="G5" t="n">
-        <v>21</v>
-      </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
     </row>
   </sheetData>
@@ -1538,12 +1723,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="n">
         <v>11</v>
       </c>
@@ -1553,17 +1740,21 @@
       <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -1573,7 +1764,9 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -1584,17 +1777,21 @@
           <t>A. Silva</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
@@ -1604,19 +1801,23 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -1628,35 +1829,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1665,63 +1866,71 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="P5" t="n">
         <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -1730,56 +1939,56 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1789,16 +1998,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1819,10 +2028,10 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1831,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1840,54 +2049,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
@@ -1895,33 +2096,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q9"/>
@@ -1935,11 +2160,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2013,8 +2238,37 @@
         <v>-13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922722</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>6.8</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>26.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (13.5)</t>
+          <t>Q4 (9.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-2.5)</t>
+          <t>Q2 (0)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 34 | fora: -13</t>
+          <t>Diff médio casa: 26.5 | fora: -13</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 34 | em derrotas: -13</t>
+          <t>Diff médio em vitórias: 26.5 | em derrotas: -13</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (13.5)</t>
+          <t>Melhor período: Q4 (9.7)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q2 (-2.5)</t>
+          <t>Pior período: Q2 (0)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Moreira sobe mais em vitórias (8 ppg).</t>
+          <t>V. Panov sobe mais em vitórias (5.5 ppg).</t>
         </is>
       </c>
     </row>
@@ -876,25 +876,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
-        <v>71</v>
+        <v>71.5</v>
       </c>
       <c r="I3" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -997,130 +997,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.3</v>
+        <v>17.3</v>
       </c>
       <c r="C2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="D2" t="n">
-        <v>16</v>
-      </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>27.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="H2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.8</v>
+        <v>15.5</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="E3" t="n">
-        <v>30.3</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>-5</v>
+        <v>-16</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>23.9</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>22.2</v>
+        <v>30.3</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H4" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="I4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="E5" t="n">
         <v>25.1</v>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -1169,44 +1169,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.7</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>27.5</v>
+        <v>22.2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="7">
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.5</v>
+        <v>20.7</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
         <v>30.8</v>
@@ -1234,10 +1234,10 @@
         <v>-5</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J7" t="n">
         <v>12</v>
@@ -1246,90 +1246,90 @@
         <v>-5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="n">
-        <v>24.1</v>
+        <v>22.7</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="J8" t="n">
         <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L8" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="M8" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.7</v>
+        <v>19.7</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="E9" t="n">
-        <v>22.7</v>
+        <v>24.1</v>
       </c>
       <c r="F9" t="n">
         <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
         <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>-7</v>
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>18.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="J3" t="n">
-        <v>23.5</v>
+        <v>21.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="H4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J5" t="n">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="K5" t="n">
-        <v>13.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1723,49 +1723,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="C2" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1774,218 +1774,218 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1998,40 +1998,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2049,46 +2049,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. Moreira</t>
+          <t>V. Panov</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>2.3</v>
+      </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
@@ -2096,50 +2104,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. Panov</t>
+          <t>A. Moreira</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2160,11 +2168,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2267,8 +2275,37 @@
         <v>34</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922728</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Vitória Sport Clube</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCB.xlsx
@@ -18,11 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>79.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-2.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (9.7)</t>
+          <t>Q4 (6.5)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (0)</t>
+          <t>Q3 (1.2)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 26.5 | fora: -13</t>
+          <t>Diff médio casa: 26.5 | fora: -2</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 26.5 | em derrotas: -13</t>
+          <t>Diff médio em vitórias: 17.8 | em derrotas: -13</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (9.7)</t>
+          <t>Melhor período: Q4 (6.5)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q2 (0)</t>
+          <t>Pior período: Q3 (1.2)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V. Panov sobe mais em vitórias (5.5 ppg).</t>
+          <t>V. Panov sobe mais em vitórias (4.3 ppg).</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -867,38 +867,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>196</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>143</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>53</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>98</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>71.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>26.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1010,19 +1043,19 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>27.5</v>
+        <v>19.3</v>
       </c>
       <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-21</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -1031,10 +1064,10 @@
         <v>-21</v>
       </c>
       <c r="L2" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -1053,19 +1086,19 @@
         <v>11.5</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
@@ -1074,96 +1107,96 @@
         <v>-16</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. Monteiro</t>
+          <t>M. Correia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.9</v>
+        <v>22.4</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="E4" t="n">
-        <v>30.3</v>
+        <v>20.9</v>
       </c>
       <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Correia</t>
+          <t>R. Monteiro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.4</v>
+        <v>23.9</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="D5" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>25.1</v>
+        <v>28.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>-11</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>-11</v>
+        <v>-5</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
@@ -1182,19 +1215,19 @@
         <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>22.2</v>
+        <v>24.6</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="H6" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I6" t="n">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="J6" t="n">
         <v>20</v>
@@ -1203,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="7">
@@ -1225,16 +1258,16 @@
         <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>15</v>
@@ -1249,93 +1282,93 @@
         <v>-4</v>
       </c>
       <c r="M7" t="n">
-        <v>-4</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E8" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="I8" t="n">
-        <v>12.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-10</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>-6</v>
+        <v>-4.5</v>
       </c>
       <c r="M8" t="n">
-        <v>-6</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="n">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>-4.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L9" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>-7</v>
+        <v>-7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1478,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="J2" t="n">
-        <v>18.7</v>
+        <v>19.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1521,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
-        <v>21.7</v>
+        <v>19.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -1531,25 +1564,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G4" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
@@ -1574,25 +1607,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="J5" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1723,43 +1756,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1778,40 +1811,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
@@ -1820,172 +1853,172 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Silva</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1998,40 +2031,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2040,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2053,34 +2086,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2089,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2108,49 +2141,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2168,11 +2201,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2304,8 +2337,37 @@
         <v>19</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922735</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CD Póvoa / Esc Online</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="n">
+        <v>71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>